--- a/PythonTesting/reports/Execution_Summary.xlsx
+++ b/PythonTesting/reports/Execution_Summary.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27 11:19:19</t>
+          <t>2026-08-27 13:36:57</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>

--- a/PythonTesting/reports/Execution_Summary.xlsx
+++ b/PythonTesting/reports/Execution_Summary.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27 13:36:57</t>
+          <t>2026-08-27 14:48:35</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
